--- a/rules/CORE-001034/negative/01/data/unit-test-coreid-CG0562-negative 1.xlsx
+++ b/rules/CORE-001034/negative/01/data/unit-test-coreid-CG0562-negative 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-001034\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753BC901-960B-4E0F-8332-BA336056A75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F0C626-EFE0-4AD5-88CA-F136DD83794A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="357" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="357" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="16" r:id="rId1"/>
@@ -579,7 +579,6 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D3AC94FD-64DC-485B-AA79-6BACF9296942}" name="Table3821" displayName="Table3821" ref="A1:W10" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
-  <autoFilter ref="A1:W10" xr:uid="{D3AC94FD-64DC-485B-AA79-6BACF9296942}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{D658CD97-7030-4E76-9717-537135449CCC}" name="STUDYID" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{31C22FC0-91C9-4FFF-9D6D-02F1C8B322E9}" name="DOMAIN" dataDxfId="21"/>
@@ -1318,13 +1317,22 @@
   <dimension ref="A1:W10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="17" max="17" width="13.85546875" customWidth="1"/>
-    <col min="20" max="20" width="15" customWidth="1"/>
-    <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1982,25 +1990,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090ADB40D834AE945B19FCDA4041AC0CB" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d36826f407302d9fd93d8089214679b0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xmlns:ns3="63ea592b-d684-45c7-8cdc-fad8f8e6bb41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="257daeb82d9c284d9d656fb5e9ad601e" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2240,26 +2229,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CB4DC7C-20D2-408C-91D6-064192CE24D0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5C4EDDE-D196-4AC8-AD02-E2439740B508}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B765E5D-323B-4EF7-A054-760F28CCF63F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2277,4 +2266,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5C4EDDE-D196-4AC8-AD02-E2439740B508}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CB4DC7C-20D2-408C-91D6-064192CE24D0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>